--- a/data/trans_orig/P36B13_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B13_R-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51592</t>
+          <t>53774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84273</t>
+          <t>85966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58552</t>
+          <t>59415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96198</t>
+          <t>94762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136956</t>
+          <t>135029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661500</t>
+          <t>659807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>694181</t>
+          <t>691999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>924167</t>
+          <t>923304</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>949014</t>
+          <t>950515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1591535</t>
+          <t>1593462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1632293</t>
+          <t>1633729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>263756</t>
+          <t>266874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331215</t>
+          <t>328439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>164180</t>
+          <t>167543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217965</t>
+          <t>216982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>443234</t>
+          <t>446440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>532833</t>
+          <t>530107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1736080</t>
+          <t>1738856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1803539</t>
+          <t>1800421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1760840</t>
+          <t>1761823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1814625</t>
+          <t>1811262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3513267</t>
+          <t>3515993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3602866</t>
+          <t>3599660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33440</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60234</t>
+          <t>60196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28285</t>
+          <t>28802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52694</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69256</t>
+          <t>68359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104214</t>
+          <t>102335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483731</t>
+          <t>483769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510525</t>
+          <t>510853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>494486</t>
+          <t>494935</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>518895</t>
+          <t>518378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>986931</t>
+          <t>988810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1021889</t>
+          <t>1022786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>379098</t>
+          <t>378611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>451152</t>
+          <t>452917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244775</t>
+          <t>242747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307670</t>
+          <t>308220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>639039</t>
+          <t>635880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>735955</t>
+          <t>737117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2905881</t>
+          <t>2904116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2977935</t>
+          <t>2978422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3201034</t>
+          <t>3200484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3263929</t>
+          <t>3265957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6129782</t>
+          <t>6128620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6226698</t>
+          <t>6229857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>40763</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50182</t>
+          <t>55479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>30953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,27 +2399,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55200</t>
+          <t>62260</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43212</t>
+          <t>47973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70760</t>
+          <t>78027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>477576</t>
+          <t>536349</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>463325</t>
+          <t>521633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488847</t>
+          <t>548618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>736239</t>
+          <t>800542</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>727339</t>
+          <t>791085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>742739</t>
+          <t>807924</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,22 +2512,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1213815</t>
+          <t>1336890</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1198255</t>
+          <t>1321123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1225803</t>
+          <t>1351177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513507</t>
+          <t>577112</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513507</t>
+          <t>577112</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513507</t>
+          <t>577112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269015</t>
+          <t>1399150</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269015</t>
+          <t>1399150</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269015</t>
+          <t>1399150</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>412612</t>
+          <t>190044</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178023</t>
+          <t>158740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1026370</t>
+          <t>226804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82882</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59366</t>
+          <t>79978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105232</t>
+          <t>118829</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>495495</t>
+          <t>288078</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249690</t>
+          <t>250643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1194569</t>
+          <t>332676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1875000</t>
+          <t>2037857</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1261242</t>
+          <t>2001097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2109589</t>
+          <t>2069161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2147942</t>
+          <t>2066238</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2125592</t>
+          <t>2045443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2171458</t>
+          <t>2084294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4022942</t>
+          <t>4104095</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3323868</t>
+          <t>4059497</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4268747</t>
+          <t>4141530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2287612</t>
+          <t>2227901</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2287612</t>
+          <t>2227901</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2287612</t>
+          <t>2227901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2230824</t>
+          <t>2164272</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2230824</t>
+          <t>2164272</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2230824</t>
+          <t>2164272</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4518437</t>
+          <t>4392173</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4518437</t>
+          <t>4392173</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4518437</t>
+          <t>4392173</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,32 +3015,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>47421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>24179</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34712</t>
+          <t>37592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51597</t>
+          <t>56281</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37530</t>
+          <t>39024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71913</t>
+          <t>74407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -3128,32 +3128,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>618608</t>
+          <t>679485</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604449</t>
+          <t>664166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629512</t>
+          <t>690733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3163,32 +3163,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>634639</t>
+          <t>708518</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>623509</t>
+          <t>695105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643732</t>
+          <t>717654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1253248</t>
+          <t>1388003</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1232932</t>
+          <t>1369877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1267315</t>
+          <t>1405260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658221</t>
+          <t>732697</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658221</t>
+          <t>732697</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658221</t>
+          <t>732697</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304845</t>
+          <t>1444284</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304845</t>
+          <t>1444284</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304845</t>
+          <t>1444284</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>476559</t>
+          <t>262909</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239512</t>
+          <t>228231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1213682</t>
+          <t>306813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>125733</t>
+          <t>143709</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99783</t>
+          <t>121441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152521</t>
+          <t>169727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>602292</t>
+          <t>406619</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357808</t>
+          <t>362552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1416189</t>
+          <t>459608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2971184</t>
+          <t>3253692</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2234061</t>
+          <t>3209788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3208231</t>
+          <t>3288370</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3518820</t>
+          <t>3575298</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3492032</t>
+          <t>3549280</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3544770</t>
+          <t>3597566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6490004</t>
+          <t>6828989</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5676107</t>
+          <t>6776000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6734488</t>
+          <t>6873056</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3447743</t>
+          <t>3516601</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3447743</t>
+          <t>3516601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3447743</t>
+          <t>3516601</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3644553</t>
+          <t>3719007</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3644553</t>
+          <t>3719007</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3644553</t>
+          <t>3719007</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7092296</t>
+          <t>7235608</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7092296</t>
+          <t>7235608</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7092296</t>
+          <t>7235608</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
